--- a/Excel Results/results_explicit.xlsx
+++ b/Excel Results/results_explicit.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.140625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -474,6 +474,11 @@
           <t>explicit_feature_4</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>explicit_feature_5</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -501,6 +506,11 @@
           <t>False</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -528,6 +538,11 @@
           <t>explicit_feature</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -555,6 +570,11 @@
           <t>img_local_context_ROI_1</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -582,6 +602,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -609,6 +634,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -636,6 +666,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -663,6 +698,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -690,6 +730,11 @@
           <t>400</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -713,6 +758,11 @@
         </is>
       </c>
       <c r="E10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -728,6 +778,7 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -739,6 +790,7 @@
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -750,6 +802,7 @@
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -777,6 +830,11 @@
           <t>27432</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>27432</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -800,6 +858,11 @@
         </is>
       </c>
       <c r="E15" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>7011</t>
         </is>
@@ -815,6 +878,7 @@
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -842,6 +906,11 @@
           <t>7011</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -869,6 +938,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -896,6 +970,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -923,6 +1002,11 @@
           <t>Embedding_Temporal_LSTM</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -946,6 +1030,11 @@
         </is>
       </c>
       <c r="E21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -961,6 +1050,7 @@
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -988,6 +1078,11 @@
           <t>head</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1015,6 +1110,11 @@
           <t>LSTM</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1042,6 +1142,11 @@
           <t>112</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1069,6 +1174,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1096,6 +1206,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1123,6 +1238,11 @@
           <t>False</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1150,6 +1270,11 @@
           <t>112</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1177,6 +1302,11 @@
           <t>0.25</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1200,6 +1330,11 @@
         </is>
       </c>
       <c r="E31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>128</t>
         </is>
@@ -1215,6 +1350,7 @@
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1242,6 +1378,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1265,6 +1406,11 @@
         </is>
       </c>
       <c r="E34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>literature_classes</t>
         </is>
@@ -1280,6 +1426,7 @@
       <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1291,6 +1438,7 @@
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1318,6 +1466,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1345,6 +1498,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1372,6 +1530,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1399,6 +1562,11 @@
           <t>0.0001</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1426,6 +1594,11 @@
           <t>1e-05</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1453,6 +1626,11 @@
           <t>Adam</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1480,6 +1658,11 @@
           <t>0.0009</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1507,6 +1690,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1534,6 +1722,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1561,6 +1754,11 @@
           <t>False</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1588,6 +1786,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1615,6 +1818,11 @@
           <t>0.1</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1642,6 +1850,11 @@
           <t>0.9</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1669,6 +1882,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1696,6 +1914,11 @@
           <t>FocalLoss</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1723,6 +1946,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1750,6 +1978,11 @@
           <t>explicit_feature_4</t>
         </is>
       </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_5</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1777,6 +2010,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1800,6 +2038,11 @@
         </is>
       </c>
       <c r="E55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1815,6 +2058,7 @@
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1826,6 +2070,7 @@
       <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1837,6 +2082,7 @@
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1848,6 +2094,7 @@
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1859,6 +2106,7 @@
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1870,6 +2118,7 @@
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1897,6 +2146,11 @@
           <t>0.841</t>
         </is>
       </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>0.843</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1924,6 +2178,11 @@
           <t>0.884</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0.884</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1951,6 +2210,11 @@
           <t>0.885</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0.885</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1978,6 +2242,11 @@
           <t>0.884</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>0.884</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2005,6 +2274,11 @@
           <t>0.882</t>
         </is>
       </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>0.883</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2032,6 +2306,11 @@
           <t>0.86</t>
         </is>
       </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>0.858</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2059,6 +2338,11 @@
           <t>0.827</t>
         </is>
       </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>0.832</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2086,6 +2370,11 @@
           <t>14</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2109,6 +2398,11 @@
         </is>
       </c>
       <c r="E70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -2124,6 +2418,7 @@
       <c r="C71" s="2" t="inlineStr"/>
       <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2151,6 +2446,11 @@
           <t>14</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2178,6 +2478,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2205,6 +2510,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2228,6 +2538,11 @@
         </is>
       </c>
       <c r="E75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2243,6 +2558,7 @@
       <c r="C76" s="2" t="inlineStr"/>
       <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="B77" s="2" t="inlineStr">
@@ -2265,6 +2581,11 @@
           <t>False</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="B78" s="2" t="inlineStr">
@@ -2287,6 +2608,11 @@
           <t>./output/dataset_cache</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="B79" s="2" t="inlineStr">
@@ -2309,6 +2635,11 @@
           <t>0.5</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="B80" s="2" t="inlineStr">
@@ -2331,6 +2662,11 @@
           <t>0.7</t>
         </is>
       </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="B81" s="2" t="inlineStr">
@@ -2353,6 +2689,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="B82" s="2" t="inlineStr">
@@ -2375,6 +2716,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="B83" s="2" t="inlineStr">
@@ -2397,6 +2743,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="B84" s="2" t="inlineStr">
@@ -2417,6 +2768,18 @@
       <c r="E84" t="inlineStr">
         <is>
           <t>5</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>0.3</t>
         </is>
       </c>
     </row>

--- a/Excel Results/results_explicit.xlsx
+++ b/Excel Results/results_explicit.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:Z85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.140625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -479,6 +479,106 @@
           <t>explicit_feature_5</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>explicit_feature_6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>explicit_feature_9</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>explicit_feature_11</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>explicit_feature_11</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>explicit_feature_13</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>explicit_feature_13</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>explicit_feature_15</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>explicit_feature_15</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>explicit_feature_16</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>explicit_feature_16</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>explicit_feature_17</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>explicit_feature_17</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>explicit_feature_18</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>explicit_feature_18</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>explicit_feature_19</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>explicit_feature_19</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>explicit_feature_20</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>explicit_feature_20</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>explicit_feature_21</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>explicit_feature_21</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -511,6 +611,106 @@
           <t>False</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -543,6 +743,106 @@
           <t>explicit_feature</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>explicit_feature</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -575,6 +875,106 @@
           <t>img_local_context_ROI_1</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>img_local_context_ROI_1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -607,6 +1007,106 @@
           <t>None</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -639,6 +1139,106 @@
           <t>None</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -671,6 +1271,106 @@
           <t>None</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,6 +1403,106 @@
           <t>1</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -735,6 +1535,106 @@
           <t>400</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -763,6 +1663,106 @@
         </is>
       </c>
       <c r="F10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -779,6 +1779,20 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -791,6 +1805,20 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -803,6 +1831,20 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -835,6 +1877,106 @@
           <t>27432</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>27432</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>27432</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7091</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7091</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7091</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>7091</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>7091</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>7091</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>27432</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>27432</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>13883</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>13883</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>9344</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>9344</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>7091</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>7091</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>27432</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>27432</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>27432</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>27432</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -863,6 +2005,106 @@
         </is>
       </c>
       <c r="F15" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1808</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1808</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1808</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1808</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>7011</t>
         </is>
@@ -879,6 +2121,20 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -911,6 +2167,106 @@
           <t>7011</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1808</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1808</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1808</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1808</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -943,6 +2299,106 @@
           <t>True</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -975,6 +2431,106 @@
           <t>None</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1007,6 +2563,106 @@
           <t>Embedding_Temporal_LSTM</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Embedding_Temporal_LSTM</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1035,6 +2691,106 @@
         </is>
       </c>
       <c r="F21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1051,6 +2807,20 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1083,6 +2853,106 @@
           <t>head</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1115,6 +2985,106 @@
           <t>LSTM</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1147,6 +3117,106 @@
           <t>112</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1179,6 +3249,106 @@
           <t>16</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1211,6 +3381,106 @@
           <t>1</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1243,6 +3513,106 @@
           <t>False</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1275,6 +3645,106 @@
           <t>112</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1307,6 +3777,106 @@
           <t>0.25</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1335,6 +3905,106 @@
         </is>
       </c>
       <c r="F31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
         <is>
           <t>128</t>
         </is>
@@ -1351,6 +4021,20 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr"/>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" t="n">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1383,6 +4067,106 @@
           <t>6</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1411,6 +4195,106 @@
         </is>
       </c>
       <c r="F34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>literature_classes</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>literature_classes</t>
         </is>
@@ -1427,6 +4311,20 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr"/>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" t="n">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1439,6 +4337,20 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr"/>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" t="n">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1471,6 +4383,106 @@
           <t>2</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1503,6 +4515,106 @@
           <t>64</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1535,6 +4647,106 @@
           <t>30</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1567,6 +4779,106 @@
           <t>0.0001</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1599,6 +4911,106 @@
           <t>1e-05</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1631,6 +5043,106 @@
           <t>Adam</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1663,6 +5175,106 @@
           <t>0.0009</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1695,6 +5307,106 @@
           <t>5</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1727,6 +5439,106 @@
           <t>5</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1759,6 +5571,106 @@
           <t>False</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1791,6 +5703,106 @@
           <t>30</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1823,6 +5835,106 @@
           <t>0.1</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1855,6 +5967,106 @@
           <t>0.9</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1887,6 +6099,106 @@
           <t>0</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1919,6 +6231,106 @@
           <t>FocalLoss</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>FocalLoss</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1951,6 +6363,106 @@
           <t>1</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1983,6 +6495,106 @@
           <t>explicit_feature_5</t>
         </is>
       </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_6</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_9</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_11</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_11</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_13</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_13</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_15</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_15</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_16</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_16</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_17</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_17</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_18</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_18</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_19</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_19</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_20</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_20</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_21</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>explicit_feature_21</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2015,6 +6627,106 @@
           <t>None</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2043,6 +6755,106 @@
         </is>
       </c>
       <c r="F55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2059,6 +6871,20 @@
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="W56" s="2" t="inlineStr"/>
+      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Z56" t="n">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2071,6 +6897,20 @@
       <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="W57" s="2" t="inlineStr"/>
+      <c r="Y57" s="2" t="inlineStr"/>
+      <c r="Z57" t="n">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2083,6 +6923,20 @@
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="W58" s="2" t="inlineStr"/>
+      <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" t="n">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2095,6 +6949,20 @@
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="W59" s="2" t="inlineStr"/>
+      <c r="Y59" s="2" t="inlineStr"/>
+      <c r="Z59" t="n">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2107,6 +6975,20 @@
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="W60" s="2" t="inlineStr"/>
+      <c r="Y60" s="2" t="inlineStr"/>
+      <c r="Z60" t="n">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2119,6 +7001,20 @@
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="W61" s="2" t="inlineStr"/>
+      <c r="Y61" s="2" t="inlineStr"/>
+      <c r="Z61" t="n">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2151,6 +7047,106 @@
           <t>0.843</t>
         </is>
       </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>0.811</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>0.804</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>0.811</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0.804</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>0.807</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0.804</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>0.824</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>0.824</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>0.816</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>0.816</t>
+        </is>
+      </c>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>0.807</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>0.804</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>0.832</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>0.832</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>0.837</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>0.837</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2183,6 +7179,106 @@
           <t>0.884</t>
         </is>
       </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>0.872</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>0.872</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>0.848</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>0.843</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>0.848</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0.843</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>0.845</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>0.842</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>0.872</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>0.872</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>0.859</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>0.859</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>0.856</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>0.856</t>
+        </is>
+      </c>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>0.845</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>0.842</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>0.871</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>0.871</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>0.881</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>0.881</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2215,6 +7311,106 @@
           <t>0.885</t>
         </is>
       </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>0.874</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>0.874</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>0.847</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>0.845</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>0.847</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0.845</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>0.844</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>0.844</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>0.874</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>0.874</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>0.859</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>0.859</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>0.864</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>0.864</t>
+        </is>
+      </c>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>0.844</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>0.844</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>0.872</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>0.872</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>0.884</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>0.884</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2247,6 +7443,106 @@
           <t>0.884</t>
         </is>
       </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>0.872</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>0.872</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>0.848</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>0.843</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>0.848</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0.843</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>0.845</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>0.842</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>0.872</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>0.872</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>0.859</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>0.859</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>0.856</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>0.856</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>0.845</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>0.842</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>0.871</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>0.871</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>0.881</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>0.881</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2279,6 +7575,106 @@
           <t>0.883</t>
         </is>
       </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>0.868</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>0.868</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>0.845</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>0.838</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>0.845</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0.838</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>0.841</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0.838</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>0.868</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>0.868</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>0.856</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>0.856</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>0.855</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>0.855</t>
+        </is>
+      </c>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>0.841</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>0.838</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>0.869</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>0.869</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>0.881</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>0.881</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2311,6 +7707,106 @@
           <t>0.858</t>
         </is>
       </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>0.864</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>0.864</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>0.832</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>0.831</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>0.832</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0.831</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0.831</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>0.864</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>0.864</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>0.846</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>0.846</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>0.846</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>0.846</t>
+        </is>
+      </c>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>0.831</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>0.855</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>0.855</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>0.854</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>0.854</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2343,6 +7839,106 @@
           <t>0.832</t>
         </is>
       </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>0.796</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>0.792</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>0.796</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0.792</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>0.793</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0.792</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>0.811</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>0.811</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>0.799</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>0.799</t>
+        </is>
+      </c>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>0.793</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>0.792</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>0.817</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>0.817</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>0.826</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>0.826</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2375,6 +7971,106 @@
           <t>14</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2403,6 +8099,106 @@
         </is>
       </c>
       <c r="F70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -2419,6 +8215,20 @@
       <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="W71" s="2" t="inlineStr"/>
+      <c r="Y71" s="2" t="inlineStr"/>
+      <c r="Z71" t="n">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2451,6 +8261,106 @@
           <t>14</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2483,6 +8393,106 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2515,6 +8525,106 @@
           <t>5</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2543,6 +8653,106 @@
         </is>
       </c>
       <c r="F75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2559,6 +8769,20 @@
       <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="W76" s="2" t="inlineStr"/>
+      <c r="Y76" s="2" t="inlineStr"/>
+      <c r="Z76" t="n">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="B77" s="2" t="inlineStr">
@@ -2586,6 +8810,106 @@
           <t>False</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="B78" s="2" t="inlineStr">
@@ -2613,6 +8937,106 @@
           <t>./output/dataset_cache</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>./output/dataset_cache</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="B79" s="2" t="inlineStr">
@@ -2640,6 +9064,106 @@
           <t>0.5</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="B80" s="2" t="inlineStr">
@@ -2667,6 +9191,106 @@
           <t>0.2</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="B81" s="2" t="inlineStr">
@@ -2694,6 +9318,106 @@
           <t>True</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="B82" s="2" t="inlineStr">
@@ -2721,6 +9445,106 @@
           <t>True</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="B83" s="2" t="inlineStr">
@@ -2748,6 +9572,106 @@
           <t>10</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="B84" s="2" t="inlineStr">
@@ -2775,11 +9699,211 @@
           <t>5</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="F85" s="2" t="inlineStr">
         <is>
           <t>0.3</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
         </is>
       </c>
     </row>
